--- a/saju-growth-system/tracking/daily-tracker.xlsx
+++ b/saju-growth-system/tracking/daily-tracker.xlsx
@@ -1,17 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="콘텐츠로그" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="판매로그" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일일요약" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="캠페인_재활성" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="안내" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="콘텐츠로그" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="주제별성과" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="판매로그" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="일일요약" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="캠페인_재활성" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -41,7 +42,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -51,6 +52,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002F3B30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF0E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -76,6 +82,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -441,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -504,41 +511,53 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>콘텐츠로그 / 판매로그 / 일일요약 / 캠페인_재활성</t>
+          <t>콘텐츠로그 / 주제별성과 / 판매로그 / 일일요약 / 캠페인_재활성</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>개인정보</t>
+          <t>주제별 측정</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>판매로그 이름은 익명코드(예: K-001) 사용. 생년월일시 등 민감정보는 여기 적지 말 것.</t>
+          <t>콘텐츠로그의 topic 열에 daily_hooks.py의 topic_id를 적으면 주제별성과 시트가 조회·참여·문의를 자동 롤업 → 1위 주제 더블다운(릴스·Shorts 확산).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>가격</t>
+          <t>개인정보</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>입문 9,900 / 코어 29,000 / 프리미엄 59,000 (옵션 궁합 +20,000·당일 +5,000)</t>
+          <t>판매로그 이름은 익명코드(예: K-001) 사용. 생년월일시 등 민감정보는 여기 적지 말 것.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>가격</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>입문 9,900 / 코어 29,000 / 프리미엄 59,000 (옵션 궁합 +20,000·당일 +5,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t>주의</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>재생성 스크립트는 덮어쓰므로 데이터 입력 후엔 백업 후 실행.</t>
         </is>
@@ -555,33 +574,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:Y2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
     <col width="7" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
     <col width="9" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="11" customWidth="1" min="21" max="21"/>
-    <col width="8" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
-    <col width="26" customWidth="1" min="24" max="24"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="26" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -597,110 +617,115 @@
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
           <t>content_id</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>hook_type</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>cta</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>link_variant</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>kakao_keyword</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>views</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>comments</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>saves</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>shares</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>profile_clicks</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>ext_link_clicks</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>kakao_inflow</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>menu_clicks</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>inquiries</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>payments</t>
         </is>
       </c>
-      <c r="S1" s="4" t="inlineStr">
+      <c r="T1" s="4" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="T1" s="4" t="inlineStr">
+      <c r="U1" s="4" t="inlineStr">
         <is>
           <t>offer</t>
         </is>
       </c>
-      <c r="U1" s="4" t="inlineStr">
+      <c r="V1" s="4" t="inlineStr">
         <is>
           <t>pdf_delivered</t>
         </is>
       </c>
-      <c r="V1" s="4" t="inlineStr">
+      <c r="W1" s="4" t="inlineStr">
         <is>
           <t>extra_q</t>
         </is>
       </c>
-      <c r="W1" s="4" t="inlineStr">
+      <c r="X1" s="4" t="inlineStr">
         <is>
           <t>repurchase</t>
         </is>
       </c>
-      <c r="X1" s="4" t="inlineStr">
+      <c r="Y1" s="4" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -712,10 +737,10 @@
     <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"threads,instagram,kakao,youtube,tiktok"</formula1>
     </dataValidation>
-    <dataValidation sqref="T2:T2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U2:U2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"입문9900,코어29000,프리미엄59000,궁합옵션,-"</formula1>
     </dataValidation>
-    <dataValidation sqref="U2:U2000 W2:W2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="V2:V2000 X2:X2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>
@@ -724,6 +749,607 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>게시수(자동)</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>총조회(자동)</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>댓글(자동)</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>공유(자동)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>외부링크(자동)</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>문의(자동)</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>결제(자동)</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>조회당참여(자동)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>money-no-keep</t>
+        </is>
+      </c>
+      <c r="B2">
+        <f>COUNTIF(콘텐츠로그!$C:$C,$A2)</f>
+        <v/>
+      </c>
+      <c r="C2">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A2,콘텐츠로그!$J:$J)</f>
+        <v/>
+      </c>
+      <c r="D2">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A2,콘텐츠로그!$K:$K)</f>
+        <v/>
+      </c>
+      <c r="E2">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A2,콘텐츠로그!$M:$M)</f>
+        <v/>
+      </c>
+      <c r="F2">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A2,콘텐츠로그!$O:$O)</f>
+        <v/>
+      </c>
+      <c r="G2">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A2,콘텐츠로그!$R:$R)</f>
+        <v/>
+      </c>
+      <c r="H2">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A2,콘텐츠로그!$S:$S)</f>
+        <v/>
+      </c>
+      <c r="I2">
+        <f>IF(C2=0,"",(D2+E2)/C2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>move-or-wait</t>
+        </is>
+      </c>
+      <c r="B3">
+        <f>COUNTIF(콘텐츠로그!$C:$C,$A3)</f>
+        <v/>
+      </c>
+      <c r="C3">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A3,콘텐츠로그!$J:$J)</f>
+        <v/>
+      </c>
+      <c r="D3">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A3,콘텐츠로그!$K:$K)</f>
+        <v/>
+      </c>
+      <c r="E3">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A3,콘텐츠로그!$M:$M)</f>
+        <v/>
+      </c>
+      <c r="F3">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A3,콘텐츠로그!$O:$O)</f>
+        <v/>
+      </c>
+      <c r="G3">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A3,콘텐츠로그!$R:$R)</f>
+        <v/>
+      </c>
+      <c r="H3">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A3,콘텐츠로그!$S:$S)</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>IF(C3=0,"",(D3+E3)/C3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>effort-no-result</t>
+        </is>
+      </c>
+      <c r="B4">
+        <f>COUNTIF(콘텐츠로그!$C:$C,$A4)</f>
+        <v/>
+      </c>
+      <c r="C4">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A4,콘텐츠로그!$J:$J)</f>
+        <v/>
+      </c>
+      <c r="D4">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A4,콘텐츠로그!$K:$K)</f>
+        <v/>
+      </c>
+      <c r="E4">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A4,콘텐츠로그!$M:$M)</f>
+        <v/>
+      </c>
+      <c r="F4">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A4,콘텐츠로그!$O:$O)</f>
+        <v/>
+      </c>
+      <c r="G4">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A4,콘텐츠로그!$R:$R)</f>
+        <v/>
+      </c>
+      <c r="H4">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A4,콘텐츠로그!$S:$S)</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>IF(C4=0,"",(D4+E4)/C4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>relationship-loop</t>
+        </is>
+      </c>
+      <c r="B5">
+        <f>COUNTIF(콘텐츠로그!$C:$C,$A5)</f>
+        <v/>
+      </c>
+      <c r="C5">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A5,콘텐츠로그!$J:$J)</f>
+        <v/>
+      </c>
+      <c r="D5">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A5,콘텐츠로그!$K:$K)</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A5,콘텐츠로그!$M:$M)</f>
+        <v/>
+      </c>
+      <c r="F5">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A5,콘텐츠로그!$O:$O)</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A5,콘텐츠로그!$R:$R)</f>
+        <v/>
+      </c>
+      <c r="H5">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A5,콘텐츠로그!$S:$S)</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>IF(C5=0,"",(D5+E5)/C5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>luck-turning-signal</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>COUNTIF(콘텐츠로그!$C:$C,$A6)</f>
+        <v/>
+      </c>
+      <c r="C6">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A6,콘텐츠로그!$J:$J)</f>
+        <v/>
+      </c>
+      <c r="D6">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A6,콘텐츠로그!$K:$K)</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A6,콘텐츠로그!$M:$M)</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A6,콘텐츠로그!$O:$O)</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A6,콘텐츠로그!$R:$R)</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A6,콘텐츠로그!$S:$S)</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>IF(C6=0,"",(D6+E6)/C6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>career-fit</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>COUNTIF(콘텐츠로그!$C:$C,$A7)</f>
+        <v/>
+      </c>
+      <c r="C7">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A7,콘텐츠로그!$J:$J)</f>
+        <v/>
+      </c>
+      <c r="D7">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A7,콘텐츠로그!$K:$K)</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A7,콘텐츠로그!$M:$M)</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A7,콘텐츠로그!$O:$O)</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A7,콘텐츠로그!$R:$R)</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A7,콘텐츠로그!$S:$S)</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>IF(C7=0,"",(D7+E7)/C7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>decision-delayed</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>COUNTIF(콘텐츠로그!$C:$C,$A8)</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A8,콘텐츠로그!$J:$J)</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A8,콘텐츠로그!$K:$K)</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A8,콘텐츠로그!$M:$M)</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A8,콘텐츠로그!$O:$O)</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A8,콘텐츠로그!$R:$R)</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A8,콘텐츠로그!$S:$S)</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IF(C8=0,"",(D8+E8)/C8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>same-saju-diff</t>
+        </is>
+      </c>
+      <c r="B9">
+        <f>COUNTIF(콘텐츠로그!$C:$C,$A9)</f>
+        <v/>
+      </c>
+      <c r="C9">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A9,콘텐츠로그!$J:$J)</f>
+        <v/>
+      </c>
+      <c r="D9">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A9,콘텐츠로그!$K:$K)</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A9,콘텐츠로그!$M:$M)</f>
+        <v/>
+      </c>
+      <c r="F9">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A9,콘텐츠로그!$O:$O)</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A9,콘텐츠로그!$R:$R)</f>
+        <v/>
+      </c>
+      <c r="H9">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A9,콘텐츠로그!$S:$S)</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>IF(C9=0,"",(D9+E9)/C9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10">
+        <f>COUNTIF(콘텐츠로그!$C:$C,$A10)</f>
+        <v/>
+      </c>
+      <c r="C10">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A10,콘텐츠로그!$J:$J)</f>
+        <v/>
+      </c>
+      <c r="D10">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A10,콘텐츠로그!$K:$K)</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A10,콘텐츠로그!$M:$M)</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A10,콘텐츠로그!$O:$O)</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A10,콘텐츠로그!$R:$R)</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A10,콘텐츠로그!$S:$S)</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>IF(C10=0,"",(D10+E10)/C10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11">
+        <f>COUNTIF(콘텐츠로그!$C:$C,$A11)</f>
+        <v/>
+      </c>
+      <c r="C11">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A11,콘텐츠로그!$J:$J)</f>
+        <v/>
+      </c>
+      <c r="D11">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A11,콘텐츠로그!$K:$K)</f>
+        <v/>
+      </c>
+      <c r="E11">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A11,콘텐츠로그!$M:$M)</f>
+        <v/>
+      </c>
+      <c r="F11">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A11,콘텐츠로그!$O:$O)</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A11,콘텐츠로그!$R:$R)</f>
+        <v/>
+      </c>
+      <c r="H11">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A11,콘텐츠로그!$S:$S)</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>IF(C11=0,"",(D11+E11)/C11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12">
+        <f>COUNTIF(콘텐츠로그!$C:$C,$A12)</f>
+        <v/>
+      </c>
+      <c r="C12">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A12,콘텐츠로그!$J:$J)</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A12,콘텐츠로그!$K:$K)</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A12,콘텐츠로그!$M:$M)</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A12,콘텐츠로그!$O:$O)</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A12,콘텐츠로그!$R:$R)</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A12,콘텐츠로그!$S:$S)</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>IF(C12=0,"",(D12+E12)/C12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13">
+        <f>COUNTIF(콘텐츠로그!$C:$C,$A13)</f>
+        <v/>
+      </c>
+      <c r="C13">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A13,콘텐츠로그!$J:$J)</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A13,콘텐츠로그!$K:$K)</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A13,콘텐츠로그!$M:$M)</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A13,콘텐츠로그!$O:$O)</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A13,콘텐츠로그!$R:$R)</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A13,콘텐츠로그!$S:$S)</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>IF(C13=0,"",(D13+E13)/C13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14">
+        <f>COUNTIF(콘텐츠로그!$C:$C,$A14)</f>
+        <v/>
+      </c>
+      <c r="C14">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A14,콘텐츠로그!$J:$J)</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A14,콘텐츠로그!$K:$K)</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A14,콘텐츠로그!$M:$M)</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A14,콘텐츠로그!$O:$O)</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A14,콘텐츠로그!$R:$R)</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A14,콘텐츠로그!$S:$S)</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>IF(C14=0,"",(D14+E14)/C14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15">
+        <f>COUNTIF(콘텐츠로그!$C:$C,$A15)</f>
+        <v/>
+      </c>
+      <c r="C15">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A15,콘텐츠로그!$J:$J)</f>
+        <v/>
+      </c>
+      <c r="D15">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A15,콘텐츠로그!$K:$K)</f>
+        <v/>
+      </c>
+      <c r="E15">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A15,콘텐츠로그!$M:$M)</f>
+        <v/>
+      </c>
+      <c r="F15">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A15,콘텐츠로그!$O:$O)</f>
+        <v/>
+      </c>
+      <c r="G15">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A15,콘텐츠로그!$R:$R)</f>
+        <v/>
+      </c>
+      <c r="H15">
+        <f>SUMIF(콘텐츠로그!$C:$C,$A15,콘텐츠로그!$S:$S)</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>IF(C15=0,"",(D15+E15)/C15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>↑ 조회 내림차순 정렬 후 1위 주제를 릴스·Shorts로 확산(repurpose.py). 신규 주제는 빈 행에 topic_id 추가.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -816,7 +1442,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1228,7 +1854,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
